--- a/tesla_Research_Report.xlsx
+++ b/tesla_Research_Report.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -55,11 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -463,13 +467,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tesla CEO Elon Musk: AI will mean everyone can have a penthouse if they … - The Times of India</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Sun, 19 Apr 2026 08:07:00 GMT</t>
-        </is>
+          <t>Stocks making the biggest moves premarket: Honeywell, Nokia, Netflix, IBM, Tesla &amp; more - CNBC</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>46135.46993055556</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -478,7 +480,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxPOXdITjE1ZjRjcmw4MUNpNzVHclo3ekoxTXdwaVpzSDFfRTZRdUJfUEFFa0hLSU05Y1gxT29Ick1WaWlOckpsNlhHU19FTm1PQnpvZHJYUkZCdzh4NGdyZThXN09XcHFyU3RSeVROajBIdzdvbkQtemQzVFlyNjJFcmVObHB2Z0dTMDBLMVFwV0tLT3RFemQ4WGctYjNVSi14eGdZN040NEJFRFNHMG1aZlhXdmhWWGhvcks5TEFUYlFfcG0tNHFpeVRrTGY4bkxJb1RHSFowVmtXWC1nSS0yZko3dllIZTE5LVHSAe8BQVVfeXFMTUNaQkZjRnJLT0l6SmMzWFNFMW9Fa2t3LWpFeGdDcW41MG9XWkd3ekJXZjBPa1EtTDVZWEoyRlhOZjdOY0o1dmtsOFBTVnMxRWcyQ3N3ak81QmtVMjM2QzZXcEJtejFrSDZSMk1PVGt1YnRzNzRBdEdnbHNUeDlJTTBTd1JVZ2tCUTdfVEtKYWlVTVdJRUNVVGdzVWpiUzRLTm53ZFhzMFlGOUZoOU1oR25kd1dsMkJJelI0bnJMWDFsQ0ZqQkNLb3UyWUcwWUgxS3RXQlBvaHBUekxNQS1DS3o0bk0yTU93aUc2YndmTlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQSmk1S016Z1VxOEwzNEVNQzFnbVV2dkxZVmpBcWFnS0d0UHBLajlXX1JWV2c1dVNEeEhhb0g1MU5iak5OWmp3NUFHZThJdnh4UDRWT0VNTmI1WV9QYm5WUmtkcjNQNDZXTVU3TzROaTJJbldROFVheGJKMkRoWjNRVllBZlpNS3NXQzdtdjc2bTJ3TXBLUno2T2pkMWVIQkhaQUE?oc=5</t>
         </is>
       </c>
     </row>
@@ -490,13 +492,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tesla brings its robotaxi service to Dallas and Houston - TechCrunch</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Sat, 18 Apr 2026 21:37:15 GMT</t>
-        </is>
+          <t>Why Fleet Operators Are Ditching Diesel for Tesla Semi – It’s All About the Money - Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>46135.6757175926</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -505,7 +505,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPdWd6cTZXTjVkcUt5cUF0MU1HVzFDc3Jyb2RuMnlrSUpFRG53bDhGdlE2NllvQkk1RjV3REFwQVptbVh2NF9vRW1mTHgtLS0xN3hBTkxQbVpyM2VEVWxtVGlMak1LbUVWa3VIZzdJTEdKT1o0blRDWGR6X1g2YUxfSUxHa1ZCblJTZG1XTzZ2X0xRV3ZT?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQZFAwRWkwNl9lbHZJMFhPSm5sWkl4Q2RtRXEtc1hxY3hqYjBnaWxYOTVMcTIzQ2RCQWg5WFBHUUpqRUx4VHBqVmxJUTNhVDM2WDJheTZJTUpXdlNJdzRRT0twdVhpenhYM2IyclRRSm54SXdvX3plVlM3dDQyMGVCdWM2WTBqQmlhdndaQmktSGFLdFpTSlVBUG1BYl9JWGUzWHc?oc=5</t>
         </is>
       </c>
     </row>
@@ -517,13 +517,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tesla expands robotaxi service to Dallas, Houston - Reuters</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Sat, 18 Apr 2026 20:41:40 GMT</t>
-        </is>
+          <t>Barclays Holds the Line on Tesla After Capex Shock: Is the Robotaxi Story Worth the Spend? - Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>46135.67585648148</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -532,7 +530,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPQmItOTJ2VDl0NVZBSVFWUWdFLWNfZU1aVVprMHN5N1hoaHZVb2kxOWpIcnEtODZldnNNS3BOT2xTbEpmNWJTQldIZFcyeDFDMHNsT29TdzFWNlh1bHZDQWxBeS1TMURMTklmZmJZOTk2MWU0S3VFcnRzN243Rk9lV090MlZlcTZNMHlTbldvS190aFBBSGFlMi1fVDZvWU1HeEhod2xlMEJWQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNelhnd2ZHOFRucEtHWVBvbWRXV2I0UzRTUHJpeUFWdnVGb2lBMTB4ck9oU1plaWt2emVIOXhlYTRVLXZleVljaFB2eGlpLW4wNXRBUXdKQmVLRDhwbk0xVmFoU1pUUHJzYUhkd0RhYnpZZ2Y5azdRZ3BDa050T19HTi1qNVNaNmtmYk5HT0tZZDVZZU9CeFRtRnAwVmw?oc=5</t>
         </is>
       </c>
     </row>
@@ -544,13 +542,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>You can now ride Tesla's robotaxis in Dallas and Houston - NewsBytes</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Sun, 19 Apr 2026 08:40:08 GMT</t>
-        </is>
+          <t>Tesla Model Y L – The Story Behind Its Aggressive Pricing - CarWale</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>46135.34376157408</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -559,7 +555,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNWWg0clN6ZDd1eGxqRFBKOWFmSDVad2h2MDd6MmhLMzUtelNydG9UUmxYLVZEaWJqMGlSYUx1T21TYW93cElrMFBBS2tlX1RjNVhkbU53Y1BuRHprWERDdU5fZzNlcGlUaXlmR05rWDVZUUY0TzZQUTkzOXpXdHh4cTF5NF9meDFIeV8wQkJRTFQ2aV9rSk1aUXNlcHBVdGEtd3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOVGozNDhwOVFEeUhxTU1ick5SNVNCaGhvMGFfWjg0alppeW9ObmlZT1pmOXJZcGV3LWxIWnlXdXc0VFVLbnVGZ3FFNm5NeGZlbzVKbUx6TS1jcUJQS1RlaWdiLW9IV2MxMGxlYmdxWm9HckFnVVZ1UUtNYXk0eFNyeUdkSUZYcURkSkxyOVpB?oc=5</t>
         </is>
       </c>
     </row>
@@ -571,22 +567,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Stock market records, Iran updates, and Tesla earnings: What to watch this week - Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Sun, 19 Apr 2026 20:31:27 GMT</t>
-        </is>
+          <t>Tesla Model Y L Launched In India At Rs 61.99 Lakh: Find FULL PRICES, Booking Details, Variants, Colours, Design, Features And More - CarDekho</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>46135.25486111111</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive / Good News</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQeHZ3TDNxVmIydmVHemMzZXFGVGtqZENxRzI3RHVCQnJYbmh3aWpOVy1uZWFTZkszSFlLd0FvclRHMk1VemY3TXNmc1FES0l1aGRBMG9XUVl0QV9vdGFtd1lRV1FKY3lhMVBPRE9Fa2thaWFEck9nY2YxTC1xeWVhZEZoNmRUUUFIeTNuQnNLVHdtZHZ6V1ZtclBxdXVDOWxrQ1dFZmJodTRVQWhscmpCeW1FdzBVNmRVaXhFZFNzYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAJBVV95cUxPcVFHdlJDYUZ5MzFablRxWjdfVk5aaWJOamIxWlppV0V6ejZKcUI5ODBScmJGb2w0eHZuanBvSTkteGgxby1pbXNHMUgwWmxxN2htdkNHVFV0Y3lHeVRFbGZha3paRjFTQndadk9nOGpkeDlmenhSWEotTkI3VExpVEU3ekdnLTEyT29xSFVBM2pFOHdnTFBSWWlORHdGT01IQzFZZWtvSk81cFhRNUpaUzJ0UHNCZFRQR2FhWDB2RkVPOWloLWM4X1BPWFJMcm81SWFoRVhXcWtPWGZ1REh2OGhXS1k1V3hOV1hGbWNqVUpxeWpzSUR3ZVltblVJVjlBRU1za9IBjAJBVV95cUxPZHEwXzJhdUZuaGI4U3JmcWtVTTFTS1luRWdQZ0ZjQ3Z4Zy1VX3dSc3lSMVhrZXpPZTE0ZFE4UWZjbnk3cWk2ZEFqTnB2RkFPbHhWV0NqSDJIMEZtQU9Nc1F2Y1BDMzZOMzAwNTdLZ1Y5VktOSWFwRFhaQ2pCdDlQc0s5QnRsVjk4YTQ5T2VTcXE4NkgxTEZrWlVuaG1oalRUcTVCV0tOblJYRzRsTzdnTGxGSU9nMkxweEk1ZXFncG1xcmFpUzFJa1RlWmpjMDZldjl3VjVsbVE4b1JxWU1VWXB5bXNucHJfaC0tSU5qN0RCazZsbVljX0dYRW41aGxmNW9hMTg0X0xndlQ3?oc=5</t>
         </is>
       </c>
     </row>
@@ -598,13 +592,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tesla Model Y Long Wheelbase to Debut in India Soon - CarWale</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Sun, 19 Apr 2026 06:08:19 GMT</t>
-        </is>
+          <t>Step aside Tesla, BYD: Japanese carmakers deepen their hold on India's auto market with hybrids - CNBC</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>46135.00972222222</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -613,7 +605,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxNOF9sWXZQOWdYZUZDejhuOC14Rm1CbFMwcnlZbWtrcXhkZWl1OUdDSlMzTWxiRGFvMUxLR2s3WXZZLXFBX085X2pWaEJNclZwUXBSSjZBdUVDMF85NkY2bTJudDRDejJWZm13bkVNdHZOeWk0T0VJS3JBNXZJSnBpWjBycVBwbFFG?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNTmR0RFJLa2wxTUhZUVB3cEQ2RnpmSXNwQkJoVEx2a1FXZW1FZjBiMUFHNF9IYUE3RHF4cDByelFjTjlidVNySm9mREJsRjduVUpocmtfQzNheW1vTDU0QkQ5MnhGMS1OWWFTdEVyN0VvRDd4R2pnTlBHQmY2UzlPUWpCVmFUbTdxZFU1WTliNU1oeW_SAZgBQVVfeXFMUG5pZ2NibGhSSjJrWVVtdHhFejZqU0pqNGw1b0xKXzR4YVFPU1I5dThGel9Jck8yZUpHeFJXM1RPRUkyQjlTb18yTkE4VVpaTDVyWmoyYmlhbjZzbTZSRjJmZ0p1NEJzbW1fUmFEazlacGxCbjltTDNVckZqY0g5NHlHUXNJMGJKYWE2RmIzcG1DdzdROS1BYkE?oc=5</t>
         </is>
       </c>
     </row>
@@ -625,22 +617,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5 big analyst AI moves: Bullish on Google stock near-term; Tesla upgraded - Investing.com India</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Sun, 19 Apr 2026 09:04:02 GMT</t>
-        </is>
+          <t>NASA Nuclear Engineer Found Dead In Burned Tesla, FBI Launches Multi-Agency Probe - NDTV</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>46135.55828703703</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive / Good News</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQVWdEMHJKajE0SjlJNjVGTnpsZUxQUHVkRHNTSW1zUHVaYi1pYm9VWDRFMVRnUDQ2RUQtbW5GRnI3V0pfcTVGZzFFaEM0RWJJRzRPOGc3VFdSRG9YakJMQ3BESVRpSWg0aTdybWJCNGdEN0c5TkJpZW1CMTVDZ2VWQ2VySGxDSTlaWHFGSlRfa2M1YWlralRob0ZaSFFxOG5YdnUzY0RLMlBraUhOM0FmRVJUTDBER3NOZXR0UVpLclEzalVj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPWElTZFp5OVVLRXNxQTFBa0hRM3lCZjRaUVE4ZFN3WDhlZGN3Nkc5aFlnOHdYRTlaakZNVW11a3l2UGRnNkhzbzV3WFg1QnMweWVJUjRfVDRlb3MyR1RzUWFMTHVsZlFvR2FXR05xM1h5c0s3cXJJbm1IaC01V3JqYUJ5YlZUSERUQTQ5Z3FkZ1VFdHJzRzduYUx2dlVGYkJTeEZETkMzazdwQzFxN2w0NkJaZE5jNV9CRVHSAcIBQVVfeXFMUERQSm5aNHdIMlZ3R09zeERhNHcxd0d6T21pSER5QkZ5M2laSURNYm83OG51RmxiV0hjdXFJcl9SS21UWk1tb2RMRjRRTU5LTGZ5dDdhU21EVTF4SFdaZGpqUnVyT2tETjg5aE5GUEdSbDFaVHU1MDVMMWd0NmdaUVhKOHZFQnpnVWxpaHVYMHpFd0lvSEo0ZHk0WGk2Tjg4dmpwZjI4UE1janpvdnVzdm90aWNwbnl0T2dhNUktSHRFWHc?oc=5</t>
         </is>
       </c>
     </row>
@@ -652,13 +642,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tesla Model Y vs Kia EV6 real world range compared - Autocar India</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Sun, 19 Apr 2026 05:30:00 GMT</t>
-        </is>
+          <t>Tesla profits up as Musk shifts focus to robotaxis - Euronews.com</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>46135.23600694445</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -667,7 +655,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOenZNQm1nalh0SXRZa1d5TWxVYUl1ejlTTlB3Q3Vma04wNWhxeWxsQU0wSW85TzBoUzlnXzQtQnBxQW55UFJDVGhGYmpBWHJtV0NzbTBKU1lIOWs2Z2VsOHpNa0NMem82RmhrUHVVNkVEWUw3RXFvOFZNcFJfZ0Z4MmQ3dHR3R0JSX1dqT1IyNEtYTWtkSDk0X2k4YjA3QWY1MEHSAacBQVVfeXFMT1lRcXN6Z2U1RkpHT2lBVjBUOUIySXZpVXFNWTVDdE9Ib3pXVUVZVl9xdEt0eExXc3MzOWp0c2J4YmxDMFZlTF85SnF4LW5ZV0tUSzgxZ01LM1NzZHN4VXJVWXpIWmF4c2VDNFJOd0E3R0dnQ3RyclhVbDNmT1pCaFh2UlNJY2ZqNlpIeHQ4OGVYZmh0Z0FsalpkZkxhbGFaWjk3QnVFc2s?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPVDdYeXNIRGViUHZoQ3lrWDJycVp0N1h5eU5STnZjOE1lWkhGMFhLVUs1Wm1pcTdqV3VOc3ZuYXBRWXJZZGlOVW0weEYxcW9TTVRDMklMNHVuZVdNSEprTGxNdjNqRlJ5aW94YlI3eDZOMU1JbFY2cVFFV0NFdGU0LTZDdWxhNGxWTkNyYVVzdFByX1RfbFZrSElkZDVBcmZUQWpBWWZta0ZpZ0xWdUxXNE1rTV94UmVwbmtHSg?oc=5</t>
         </is>
       </c>
     </row>
@@ -679,13 +667,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tesla hits 0% charge in remote Chilean desert as YouTuber uses hood-mounted solar - Interesting Engineering</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Sun, 19 Apr 2026 10:35:00 GMT</t>
-        </is>
+          <t>Musk Offers Amends for Teslas Lacking the Ability to Self-Drive - Bloomberg.com</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>46135.50460648148</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -694,7 +680,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxQa1pTNHgwMEYxRkxTS3dNY0JWakpNakJSZFZGcVV3ZGZQbXpwWVZ2djRnT1lTUW9zeXhlTmhJUG5JeGJDTUlDLTZjUkl6NVBqbmIzOTFqZ0EwRTdjbTV0LURhTFpaZkUxOUxwVmFYakNDRDlvdnB3eFo5THlPVlJpLVRlenQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPQzVMa1hXMng0UVRyM0ppZlF1bDVxbEpPS2cxR3UtSElDWE52U3FwYlhzTU40SHhuVzJlQjhCMG16Z2pPeXhTUDQtaGxlOTZOcHV3cE5sUmE2NlM4bHo0VU5mak1HNVAxbVhtMDQ2ODVCZTJOWEhLdGZxY2JPSXhQaW5NVEZlRHhBczJJbTVDdHNZYWNGYVF2MmZ4SnkxZC1mOE1DZWs2cDJvR1JYWVR3?oc=5</t>
         </is>
       </c>
     </row>
@@ -706,13 +692,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>How Tesla’s Valuation Surges To $2 Trillion - Forbes</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Fri, 17 Apr 2026 12:10:19 GMT</t>
-        </is>
+          <t>Elon Musk's Optimus dream inches closer to reality - Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>46134.97207175926</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -721,7 +705,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQUEF5UzdmeHh6bjRSZXVwclRLYU42RzB5dWxrc0J0NVFIRmE5eTZjZVlZbWVQdVVxS2phNzQxTzBXclBvMUNsdm5maE9oNUx4OGQzNXVOSGZucTBFc2JudmxBU0w5Q2R1VE9qamFTVVR3Yjg3STRSeDZkOGpGbzl4UW1PY0g1WjIyMlBJaVdrTkVHQ2ZXSndnTGJmNkdhX3Fid2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPWU04ZzZRRjFEdTVBSkJyU2d6MlVfSmVIek5oSjJQaVU4RnpsVkMwWXRWbWhKUmFlQ2o4VURaVFBUdWxEUFlCYXF0eXp4R3EzcGZaV1d3RFg3MG8xVW5RYnREeHhlQlVUdXUyaWxBemlvTE5jcHFLdmp6QlFwaHdzSjZBR29LNm45eTZLVVlNSi1DX0dNQ1B4cGdxUlRheEkyS1JGVXNCc1RJajdwTGpEcmxZUQ?oc=5</t>
         </is>
       </c>
     </row>
